--- a/output/pdf_financials_xlsx/FRDM.xlsx
+++ b/output/pdf_financials_xlsx/FRDM.xlsx
@@ -2201,16 +2201,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.223227</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.352877</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.118906</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.33285</v>
       </c>
     </row>
     <row r="93">
@@ -2683,16 +2683,16 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.3655</v>
+        <v>0.202806</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>1.205</v>
+        <v>0.447751</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.309628</v>
+        <v>-0.8809979999999999</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.441101</v>
+        <v>-0.868382</v>
       </c>
     </row>
     <row r="119">
@@ -3628,7 +3628,11 @@
           <t>Reserve 5</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>0.223227</v>
       </c>
@@ -4420,7 +4424,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>-0.162694</v>
       </c>

--- a/output/pdf_financials_xlsx/FRDM.xlsx
+++ b/output/pdf_financials_xlsx/FRDM.xlsx
@@ -1083,16 +1083,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.036629</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.369675</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.162793</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.02405</v>
       </c>
     </row>
     <row r="35">
@@ -1121,16 +1121,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.036629</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.0125</v>
+        <v>0.382175</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.0125</v>
+        <v>1.175293</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.0125</v>
+        <v>0.03655</v>
       </c>
     </row>
     <row r="37">
@@ -1349,16 +1349,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.036629</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.206212</v>
+        <v>0.836537</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.172771</v>
+        <v>0.009978000000000001</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.073404</v>
+        <v>0.049354</v>
       </c>
     </row>
     <row r="49">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/FRDM.xlsx
+++ b/output/pdf_financials_xlsx/FRDM.xlsx
@@ -3980,7 +3980,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
